--- a/data/trans_dic/P79$impuestos_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P79$impuestos_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,88</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,23</t>
+          <t>0,2; 2,39</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,43</t>
+          <t>0,26; 3,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,34</t>
+          <t>0,23; 1,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,38</t>
+          <t>0,41; 2,2</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,22</t>
+          <t>0,33; 2,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,6</t>
+          <t>0,83; 2,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,0</t>
+          <t>0,73; 1,93</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,27</t>
+          <t>0,68; 2,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,14</t>
+          <t>0,87; 2,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,79</t>
+          <t>0,95; 2,26</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,07</t>
+          <t>1,54; 3,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,14</t>
+          <t>0,58; 2,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,69</t>
+          <t>1,24; 2,71</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,33</t>
+          <t>0,39; 2,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,22</t>
+          <t>0,94; 2,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,86</t>
+          <t>0,87; 2,16</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,06</t>
+          <t>0,6; 3,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,61</t>
+          <t>0,27; 1,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,71</t>
+          <t>0,52; 1,68</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,76</t>
+          <t>1,0; 1,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,53</t>
+          <t>0,93; 1,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 1,47</t>
+          <t>1,07; 1,63</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5948</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 10905</t>
+          <t>0; 12130</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 11222</t>
+          <t>0; 12194</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1527; 14731</t>
+          <t>1455; 17102</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>9172</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1293; 14271</t>
+          <t>1228; 16791</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1028; 10066</t>
+          <t>1092; 9079</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3396; 20172</t>
+          <t>3902; 20991</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>15189</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1355; 11605</t>
+          <t>1996; 12389</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4691; 15040</t>
+          <t>5011; 15574</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7984; 22060</t>
+          <t>8830; 23286</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>20191</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2892; 19847</t>
+          <t>4665; 18254</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4949; 14847</t>
+          <t>6241; 17064</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9531; 28092</t>
+          <t>13330; 31614</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>21878</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8267; 22185</t>
+          <t>9090; 23487</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3173; 11233</t>
+          <t>3397; 11970</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13176; 28781</t>
+          <t>14621; 31955</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>11610</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1764; 8401</t>
+          <t>1530; 9113</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1935; 13267</t>
+          <t>4002; 12167</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4567; 17785</t>
+          <t>7186; 17786</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7425</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1509; 8488</t>
+          <t>1834; 9412</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1068; 6544</t>
+          <t>1190; 6612</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3253; 11660</t>
+          <t>3878; 12529</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30468; 59263</t>
+          <t>34229; 63593</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28652; 53784</t>
+          <t>33638; 58000</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>64779; 100895</t>
+          <t>75265; 114533</t>
         </is>
       </c>
     </row>
